--- a/sheets/대금율보/검수/북간도 아리랑.xlsx
+++ b/sheets/대금율보/검수/북간도 아리랑.xlsx
@@ -5600,56 +5600,45 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹)
-‹</t>
+          <t xml:space="preserve">浹)</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹)
-‹</t>
+          <t xml:space="preserve">浹)</t>
         </is>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹)
-‹</t>
+          <t xml:space="preserve">浹)</t>
         </is>
       </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N12" s="21"/>
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹)
-‹</t>
+          <t xml:space="preserve">浹)</t>
         </is>
       </c>
       <c r="Q12" s="22"/>

--- a/sheets/대금율보/검수/북간도 아리랑.xlsx
+++ b/sheets/대금율보/검수/북간도 아리랑.xlsx
@@ -4926,28 +4926,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.84" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.84" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
       <c r="P14" s="21"/>
       <c r="Q14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -6104,7 +6104,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.84" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6123,7 +6123,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.84" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -6188,6 +6188,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>